--- a/data/daily/2026-08/2026-08-29.xlsx
+++ b/data/daily/2026-08/2026-08-29.xlsx
@@ -1170,14 +1170,39 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1192,17 +1217,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="352425" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1242,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,17 +1267,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="323850" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,17 +1317,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1292,17 +1342,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1317,60 +1367,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -1425,52 +1425,77 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="952500" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1478,49 +1503,74 @@
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="866775" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1528,104 +1578,54 @@
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -2731,7 +2731,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2739,34 +2739,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>올인원 명품비타민 이뮨 멀티비타민 미네랄 7입+비타민젤리 마시는 액상 종합 비타민 수험생 직장인 부모님 건강 선물</t>
+          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>정관장</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>21,900원</t>
+          <t>35,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7948462</t>
+          <t>https://gift.kakao.com/product/12159594</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260814153548_9829675ac5e14db383c0dd63450e48bc.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260812135521_25667cc1efc34a698d1813fe75189344.jpg</t>
         </is>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2774,34 +2774,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
+          <t>올인원 명품비타민 이뮨 멀티비타민 미네랄 7입+비타민젤리 마시는 액상 종합 비타민 수험생 직장인 부모님 건강 선물</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>정관장</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>35,000원</t>
+          <t>21,900원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12159594</t>
+          <t>https://gift.kakao.com/product/7948462</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260812135521_25667cc1efc34a698d1813fe75189344.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260814153548_9829675ac5e14db383c0dd63450e48bc.jpg</t>
         </is>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2809,34 +2809,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
+          <t>오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>52,900원</t>
+          <t>59,800원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10903147</t>
+          <t>https://gift.kakao.com/product/8167919</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260601193534_8d89165f65364cb0b3c77a98481c17d6.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260824090746_aecda274677840e2bce6fa7e201e1caa.jpg</t>
         </is>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2844,27 +2844,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
+          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>59,800원</t>
+          <t>52,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/8167919</t>
+          <t>https://gift.kakao.com/product/10903147</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260824090746_aecda274677840e2bce6fa7e201e1caa.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260601193534_8d89165f65364cb0b3c77a98481c17d6.jpg</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
     <row r="14" ht="38" customHeight="1">
       <c r="B14" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2949,34 +2949,34 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[헬로키티 한정판/단독] 리유저블백&amp;틴케이스 키링 증정, 엑스트라버진 올리브오일 캡슐 30포</t>
+          <t>2입 추가 증정 "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>아일로</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>29,900원</t>
+          <t>65,900원</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11839566</t>
+          <t>https://gift.kakao.com/product/4965835</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260820175751_c5d7886f2f9642b8b4b4d5e38061f2bc.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260703103417_e8e422c5cf9740e3bfc2662a9aaa1eef.jpg</t>
         </is>
       </c>
     </row>
     <row r="15" ht="38" customHeight="1">
       <c r="B15" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2984,27 +2984,27 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2입 추가 증정 "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
+          <t>[헬로키티 한정판/단독] 리유저블백&amp;틴케이스 키링 증정, 엑스트라버진 올리브오일 캡슐 30포</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>아일로</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>65,900원</t>
+          <t>29,900원</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/4965835</t>
+          <t>https://gift.kakao.com/product/11839566</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260703103417_e8e422c5cf9740e3bfc2662a9aaa1eef.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260820175751_c5d7886f2f9642b8b4b4d5e38061f2bc.jpg</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
     <row r="19" ht="38" customHeight="1">
       <c r="B19" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -3124,34 +3124,34 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1+베리오트바 2EA</t>
+          <t>BEST 프로틴모음 [랩노쉬] 프로틴 락커 12종 선물세트 (프로틴 드링크 퍼펙트, 단백쿠키, 단백 쿠키바)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>셀렉스</t>
+          <t>랩노쉬</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>27,900원</t>
+          <t>20,900원</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13550266</t>
+          <t>https://gift.kakao.com/product/12052312</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260818144856_50ab1e34a7b8444cba1a8c0c7ec0ffce.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260723171929_09161ef5007a47039ea2ea7988556deb.jpg</t>
         </is>
       </c>
     </row>
     <row r="20" ht="38" customHeight="1">
       <c r="B20" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -3159,27 +3159,27 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BEST 프로틴모음 [랩노쉬] 프로틴 락커 12종 선물세트 (프로틴 드링크 퍼펙트, 단백쿠키, 단백 쿠키바)</t>
+          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1+베리오트바 2EA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>랩노쉬</t>
+          <t>셀렉스</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>20,900원</t>
+          <t>27,900원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12052312</t>
+          <t>https://gift.kakao.com/product/13550266</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260723171929_09161ef5007a47039ea2ea7988556deb.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260818144856_50ab1e34a7b8444cba1a8c0c7ec0ffce.jpg</t>
         </is>
       </c>
     </row>
@@ -3359,22 +3359,22 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
+          <t>홍삼/인삼</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
           <t>멀티비타민/종합비타민</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>홍삼/인삼</t>
-        </is>
-      </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
           <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
     </row>
@@ -3416,22 +3416,22 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>정관장</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>종근당</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>정관장</t>
-        </is>
-      </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
+          <t>오쏘몰</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
           <t>닥터블릿</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
+          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
           <t>올인원 명품비타민 이뮨 멀티비타민 미네랄 7입+비타민젤리 마시는 액상 종합 비타민 수험생 직장인 부모님 건강 선물</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
-        </is>
-      </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
+          <t>오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
           <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
     </row>
@@ -3530,22 +3530,22 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
+          <t>35,000원</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
           <t>21,900원</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>35,000원</t>
-        </is>
-      </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
+          <t>59,800원</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
           <t>52,900원</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>59,800원</t>
         </is>
       </c>
     </row>
@@ -3698,14 +3698,14 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
@@ -3723,12 +3723,12 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -3755,14 +3755,14 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
+          <t>아일로</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
           <t>푸드올로지</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>아일로</t>
-        </is>
-      </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
           <t>한끼통살</t>
@@ -3780,12 +3780,12 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>랩노쉬</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
           <t>셀렉스</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>랩노쉬</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -3812,14 +3812,14 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
+          <t>2입 추가 증정 "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
           <t>[헬로키티 한정판/단독] 리유저블백&amp;틴케이스 키링 증정, 엑스트라버진 올리브오일 캡슐 30포</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>2입 추가 증정 "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
-        </is>
-      </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
           <t>[한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
@@ -3837,12 +3837,12 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>BEST 프로틴모음 [랩노쉬] 프로틴 락커 12종 선물세트 (프로틴 드링크 퍼펙트, 단백쿠키, 단백 쿠키바)</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
           <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1+베리오트바 2EA</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>BEST 프로틴모음 [랩노쉬] 프로틴 락커 12종 선물세트 (프로틴 드링크 퍼펙트, 단백쿠키, 단백 쿠키바)</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -3869,14 +3869,14 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
+          <t>65,900원</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
           <t>29,900원</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>65,900원</t>
-        </is>
-      </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
           <t>45,800원</t>
@@ -3894,12 +3894,12 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>20,900원</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
           <t>27,900원</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>20,900원</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -4077,19 +4077,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260624/m6tznB24o1VYvw4vwVs3613602085_00_00m6tznB24o1VYvw4vwVs3.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>종근당건강 락토조이 오늘비움 3병 3일분</t>
+          <t>유한양행 장건강 생유산균 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>유한양행</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -4112,19 +4112,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591555314&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651649&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260428/PgvB4Sjc4dtxAp5jXpwI591555314_00_01PgvB4Sjc4dtxAp5jXpwI.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260325/RN6BLb2wWdxkL0nu9aVK600651649_00_00RN6BLb2wWdxkL0nu9aVK.jpg</t>
         </is>
       </c>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>혈행</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4132,27 +4132,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
         </is>
       </c>
     </row>
@@ -4194,7 +4194,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4202,34 +4202,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비비랩 애사비 탱글 포켓 젤리 사과맛 5포 5일분</t>
+          <t>동국제약 혈당케어＆유산균 30캡슐</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>비비랩 (BB LAB)</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994852703&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910678&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260615/tjVLFd8X16oPgAvdvPpK994852703_00_00tjVLFd8X16oPgAvdvPpK.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250829/y6DqUAmlgLsAXGUrvbmN610910678_00_00y6DqUAmlgLsAXGUrvbmN.png</t>
         </is>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>동화 바이마그랩 마그네슘 식이섬유 5포 5일분</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4252,19 +4252,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618642&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260406/wJCESiflDyulw8oZ8pW1601618642_00_00wJCESiflDyulw8oZ8pW1.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
         </is>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>동국제약 마데카 리포좀 글루타치온C 20포</t>
+          <t>안국약품 토비콤 루테인 지아잔틴 24캡슐</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -4287,19 +4287,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910602&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=611982830&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250526/v8Ijysy1W7JDCZhMJsLi610910602_00_00v8Ijysy1W7JDCZhMJsLi.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250623/xCRETYTkHbPblUcjT18I611982830_00_00xCRETYTkHbPblUcjT18I.jpg</t>
         </is>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>오브맘 비타민D＆아연 하루구미 30일분</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -4322,19 +4322,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602130&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250922/dxtu28UFPhWKbi5IG3n8613602130_00_01dxtu28UFPhWKbi5IG3n8.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260624/m6tznB24o1VYvw4vwVs3613602085_00_00m6tznB24o1VYvw4vwVs3.jpg</t>
         </is>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>대웅제약 칼슘 120정 30일분</t>
+          <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4357,19 +4357,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000147&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000203&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250409/7vBQfmyyR1zN9NfVg993600000147_00_007vBQfmyyR1zN9NfVg993.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20251202/7FdyxsWTlcbRJnDROGoC600000203_00_007FdyxsWTlcbRJnDROGoC.jpg</t>
         </is>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>종근당건강 눈건강엔 루테인지아잔틴</t>
+          <t>유한양행 산뜻해질 생유산균 20캡슐 20일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>유한양행</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -4392,12 +4392,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591580541&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651654&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250430/yuK2zGjcuX8RmMDP9k9P591580541_00_00yuK2zGjcuX8RmMDP9k9P.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260325/BJcWNz19ajlLYaMbOK0e600651654_00_00BJcWNz19ajlLYaMbOK0e.jpg</t>
         </is>
       </c>
     </row>
@@ -4512,52 +4512,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>혈행</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>마그네슘</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>비타민D</t>
-        </is>
-      </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
     </row>
@@ -4569,52 +4569,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>유한양행</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>안국약품</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>안국약품</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>닥터블릿</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>종근당건강</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>안국약품</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>비비랩 (BB LAB)</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>동화약품</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>동국제약</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>오브맘</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>유한양행</t>
         </is>
       </c>
     </row>
@@ -4626,52 +4626,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>유한양행 장건강 생유산균 30캡슐 30일분</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>동국제약 혈당케어＆유산균 30캡슐</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>안국약품 토비콤 루테인 지아잔틴 24캡슐</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
           <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>종근당건강 락토조이 오늘비움 3병 3일분</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>비비랩 애사비 탱글 포켓 젤리 사과맛 5포 5일분</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>동화 바이마그랩 마그네슘 식이섬유 5포 5일분</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>동국제약 마데카 리포좀 글루타치온C 20포</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>오브맘 비타민D＆아연 하루구미 30일분</t>
-        </is>
-      </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 칼슘 120정 30일분</t>
+          <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>종근당건강 눈건강엔 루테인지아잔틴</t>
+          <t>유한양행 산뜻해질 생유산균 20캡슐 20일분</t>
         </is>
       </c>
     </row>
@@ -4693,17 +4693,17 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
+          <t>2,000원</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -4902,7 +4902,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4910,27 +4910,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[8월 올영픽/한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>[8월 올영픽/덴프스] 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>32,900원</t>
+          <t>31,900원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549616ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265832ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -4945,34 +4945,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[8월 올영픽/파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
+          <t>[8월 올영픽/한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>11,900원</t>
+          <t>32,900원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364585ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549616ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4980,27 +4980,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[8월 올영픽/감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[8월 올영픽] 오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>16,900원</t>
+          <t>55,900원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355463ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308653ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -5015,12 +5015,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[웰니스 루틴] 온리추얼 슬리밍컷 다이어트/리셋 브이라인/글로우업 콜라겐 7포(+1포)/14포 (8/14일분)</t>
+          <t>[8월 올영픽/파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>온리추얼</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5030,19 +5030,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000236701&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023670136ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364585ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5050,34 +5050,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[8월 올영픽] 오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+          <t>고려은단 메가도스C 비타민C 3000mg 100포 (100일분)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>55,900원</t>
+          <t>25,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225906&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308653ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022590605ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5085,27 +5085,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[8월 올영픽/덴프스] 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>[8월 올영픽/1일 1정] 바이탈뷰티 메타그린 슬림업 30일 (+15일)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>바이탈뷰티</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>31,900원</t>
+          <t>29,300원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000248462&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265832ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024846227ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -5120,27 +5120,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[8월 올영픽] 락토핏 골드 트리플 기획 (3개월분)</t>
+          <t>[곽민경 PICK] 생활약속 기분전환 10포+1포 증정기획 (알파플러스, 오리지널)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>락토핏</t>
+          <t>생활약속</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>19,900원</t>
+          <t>14,500원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000199062&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019906245ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012131ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -5155,34 +5155,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[곽민경 PICK] 생활약속 기분전환 10포+1포 증정기획 (알파플러스, 오리지널)</t>
+          <t>[올영단독 증량기획] 셀트리온 홀드잇 매드 MAD 10일 (+2일)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>생활약속</t>
+          <t>이너랩</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>14,500원</t>
+          <t>18,900원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000254467&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012131ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025446723ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5190,27 +5190,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>[8월 올영픽/감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>16,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355463ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -5330,34 +5330,34 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
     </row>
@@ -5387,47 +5387,47 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>프로뉴트리션</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>오쏘몰</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>푸드올로지</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>바이탈뷰티</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>생활약속</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>이너랩</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>멜라메이트</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>온리추얼</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>덴프스</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>락토핏</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>생활약속</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터</t>
         </is>
       </c>
     </row>
@@ -5444,47 +5444,47 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>[8월 올영픽/덴프스] 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>[8월 올영픽/한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>[8월 올영픽] 오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>[8월 올영픽/파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>고려은단 메가도스C 비타민C 3000mg 100포 (100일분)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>[8월 올영픽/1일 1정] 바이탈뷰티 메타그린 슬림업 30일 (+15일)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>[곽민경 PICK] 생활약속 기분전환 10포+1포 증정기획 (알파플러스, 오리지널)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>[올영단독 증량기획] 셀트리온 홀드잇 매드 MAD 10일 (+2일)</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>[8월 올영픽/감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>[웰니스 루틴] 온리추얼 슬리밍컷 다이어트/리셋 브이라인/글로우업 콜라겐 7포(+1포)/14포 (8/14일분)</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>[8월 올영픽] 오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[8월 올영픽/덴프스] 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>[8월 올영픽] 락토핏 골드 트리플 기획 (3개월분)</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>[곽민경 PICK] 생활약속 기분전환 10포+1포 증정기획 (알파플러스, 오리지널)</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
     </row>
@@ -5501,47 +5501,47 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
+          <t>31,900원</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
           <t>32,900원</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>55,900원</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>11,900원</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>25,900원</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>29,300원</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>14,500원</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>18,900원</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>16,900원</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>11,900원</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>55,900원</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>31,900원</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>19,900원</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>14,500원</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>27,400원</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5667,20 +5667,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>35</v>
+        <v>27.5</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
         <v>3</v>
@@ -5689,20 +5689,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>22.5</v>
+        <v>27.5</v>
       </c>
       <c r="D3" t="n">
         <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
         <v>4</v>
@@ -5737,38 +5737,38 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5834,16 +5834,16 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
         <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5859,28 +5859,6 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>혈행</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
         <v>0</v>
       </c>
     </row>
